--- a/缓存数据/concat_area_csm_zz.xlsx
+++ b/缓存数据/concat_area_csm_zz.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>223566.6300000001</v>
+        <v>245507.75</v>
       </c>
       <c r="C2" t="n">
-        <v>69251.75999999999</v>
+        <v>68267.14999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>67156.91999999998</v>
+        <v>63474.53999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>2094.84</v>
+        <v>4792.609999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>56554.38999999997</v>
+        <v>52882.57000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>12697.37</v>
+        <v>15384.58000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>771.86</v>
+        <v>828.92</v>
       </c>
       <c r="I2" t="n">
-        <v>154314.8700000001</v>
+        <v>177240.6</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245507.7499999999</v>
+        <v>252574.7700000002</v>
       </c>
       <c r="C3" t="n">
-        <v>68267.14999999998</v>
+        <v>72673.95999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>63474.53999999999</v>
+        <v>65001.86000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4792.61</v>
+        <v>7672.1</v>
       </c>
       <c r="F3" t="n">
-        <v>52882.57000000001</v>
+        <v>54232.25</v>
       </c>
       <c r="G3" t="n">
-        <v>15384.58000000001</v>
+        <v>18441.71000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>828.9200000000001</v>
+        <v>838.01</v>
       </c>
       <c r="I3" t="n">
-        <v>177240.5999999999</v>
+        <v>179900.8100000002</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>252574.77</v>
+        <v>226817.77</v>
       </c>
       <c r="C4" t="n">
-        <v>72673.95999999995</v>
+        <v>69444.26000000005</v>
       </c>
       <c r="D4" t="n">
-        <v>65001.86</v>
+        <v>61963.48000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>7672.100000000001</v>
+        <v>7480.780000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>54232.25</v>
+        <v>52585.21000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>18441.71</v>
+        <v>16859.05</v>
       </c>
       <c r="H4" t="n">
-        <v>838.01</v>
+        <v>858.0800000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>179900.8100000001</v>
+        <v>157373.5099999999</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>226817.77</v>
+        <v>212851.34</v>
       </c>
       <c r="C5" t="n">
-        <v>69444.26000000007</v>
+        <v>66833.92999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>61963.48000000001</v>
+        <v>61168.39</v>
       </c>
       <c r="E5" t="n">
-        <v>7480.780000000001</v>
+        <v>5665.539999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>52585.21000000001</v>
+        <v>52413.57999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>16859.05</v>
+        <v>14420.35</v>
       </c>
       <c r="H5" t="n">
-        <v>858.0800000000002</v>
+        <v>810.3699999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>157373.5099999999</v>
+        <v>146017.41</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>212851.3400000001</v>
+        <v>224958.2700000001</v>
       </c>
       <c r="C6" t="n">
-        <v>66833.93000000002</v>
+        <v>65997.15000000002</v>
       </c>
       <c r="D6" t="n">
-        <v>61168.39000000001</v>
+        <v>62811.30000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>5665.539999999999</v>
+        <v>3185.85</v>
       </c>
       <c r="F6" t="n">
-        <v>52413.57999999999</v>
+        <v>51556.69</v>
       </c>
       <c r="G6" t="n">
-        <v>14420.35</v>
+        <v>14440.45999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>810.37</v>
+        <v>1111.65</v>
       </c>
       <c r="I6" t="n">
-        <v>146017.41</v>
+        <v>158961.1200000001</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224958.2700000001</v>
+        <v>206469.09</v>
       </c>
       <c r="C7" t="n">
-        <v>65997.15000000001</v>
+        <v>62442.81</v>
       </c>
       <c r="D7" t="n">
-        <v>62811.3</v>
+        <v>61650.59999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3185.849999999999</v>
+        <v>792.21</v>
       </c>
       <c r="F7" t="n">
-        <v>51556.69</v>
+        <v>50108.55000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>14440.46</v>
+        <v>12334.26000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1111.65</v>
+        <v>1132.61</v>
       </c>
       <c r="I7" t="n">
-        <v>158961.1200000001</v>
+        <v>144026.28</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>206469.09</v>
+        <v>232719.43</v>
       </c>
       <c r="C8" t="n">
-        <v>62442.81</v>
+        <v>64810.07000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>61650.59999999999</v>
+        <v>64513.37000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>792.21</v>
+        <v>296.7</v>
       </c>
       <c r="F8" t="n">
-        <v>50108.55000000002</v>
+        <v>52074.94999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>12334.26000000001</v>
+        <v>12735.12</v>
       </c>
       <c r="H8" t="n">
-        <v>1132.61</v>
+        <v>1139.99</v>
       </c>
       <c r="I8" t="n">
-        <v>144026.28</v>
+        <v>167909.36</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232719.4300000001</v>
+        <v>239462.8699999999</v>
       </c>
       <c r="C9" t="n">
-        <v>64810.07000000003</v>
+        <v>67639.74999999996</v>
       </c>
       <c r="D9" t="n">
-        <v>64513.37000000003</v>
+        <v>67335.08999999994</v>
       </c>
       <c r="E9" t="n">
-        <v>296.7</v>
+        <v>304.66</v>
       </c>
       <c r="F9" t="n">
-        <v>52074.94999999999</v>
+        <v>55129.07</v>
       </c>
       <c r="G9" t="n">
-        <v>12735.12</v>
+        <v>12510.68</v>
       </c>
       <c r="H9" t="n">
-        <v>1139.99</v>
+        <v>1089.22</v>
       </c>
       <c r="I9" t="n">
-        <v>167909.3600000001</v>
+        <v>171823.1199999999</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/concat_area_csm_zz.xlsx
+++ b/缓存数据/concat_area_csm_zz.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>245507.75</v>
+        <v>243734.0500000001</v>
       </c>
       <c r="C2" t="n">
-        <v>68267.14999999999</v>
+        <v>84890.52000000005</v>
       </c>
       <c r="D2" t="n">
-        <v>63474.53999999999</v>
+        <v>84500.63000000006</v>
       </c>
       <c r="E2" t="n">
-        <v>4792.609999999999</v>
+        <v>389.89</v>
       </c>
       <c r="F2" t="n">
-        <v>52882.57000000001</v>
+        <v>68616.70999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>15384.58000000001</v>
+        <v>16273.81</v>
       </c>
       <c r="H2" t="n">
-        <v>828.92</v>
+        <v>406.09</v>
       </c>
       <c r="I2" t="n">
-        <v>177240.6</v>
+        <v>158843.53</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>252574.7700000002</v>
+        <v>243110.3899999999</v>
       </c>
       <c r="C3" t="n">
-        <v>72673.95999999999</v>
+        <v>86213.23000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>65001.86000000001</v>
+        <v>85628.52999999998</v>
       </c>
       <c r="E3" t="n">
-        <v>7672.1</v>
+        <v>584.7</v>
       </c>
       <c r="F3" t="n">
-        <v>54232.25</v>
+        <v>67987.29000000002</v>
       </c>
       <c r="G3" t="n">
-        <v>18441.71000000001</v>
+        <v>18225.94</v>
       </c>
       <c r="H3" t="n">
-        <v>838.01</v>
+        <v>393.95</v>
       </c>
       <c r="I3" t="n">
-        <v>179900.8100000002</v>
+        <v>156897.1599999999</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>226817.77</v>
+        <v>232549.2300000001</v>
       </c>
       <c r="C4" t="n">
-        <v>69444.26000000005</v>
+        <v>76748.73000000004</v>
       </c>
       <c r="D4" t="n">
-        <v>61963.48000000001</v>
+        <v>76397.29000000002</v>
       </c>
       <c r="E4" t="n">
-        <v>7480.780000000001</v>
+        <v>351.44</v>
       </c>
       <c r="F4" t="n">
-        <v>52585.21000000001</v>
+        <v>63465.18999999997</v>
       </c>
       <c r="G4" t="n">
-        <v>16859.05</v>
+        <v>13283.54</v>
       </c>
       <c r="H4" t="n">
-        <v>858.0800000000002</v>
+        <v>435.73</v>
       </c>
       <c r="I4" t="n">
-        <v>157373.5099999999</v>
+        <v>155800.5000000001</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212851.34</v>
+        <v>234771.82</v>
       </c>
       <c r="C5" t="n">
-        <v>66833.92999999999</v>
+        <v>78813.70000000004</v>
       </c>
       <c r="D5" t="n">
-        <v>61168.39</v>
+        <v>78665.68000000004</v>
       </c>
       <c r="E5" t="n">
-        <v>5665.539999999998</v>
+        <v>148.02</v>
       </c>
       <c r="F5" t="n">
-        <v>52413.57999999999</v>
+        <v>67560.58000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>14420.35</v>
+        <v>11253.12</v>
       </c>
       <c r="H5" t="n">
-        <v>810.3699999999999</v>
+        <v>401.49</v>
       </c>
       <c r="I5" t="n">
-        <v>146017.41</v>
+        <v>155958.12</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>224958.2700000001</v>
+        <v>212992.2700000001</v>
       </c>
       <c r="C6" t="n">
-        <v>65997.15000000002</v>
+        <v>76834.53000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>62811.30000000002</v>
+        <v>76753.83</v>
       </c>
       <c r="E6" t="n">
-        <v>3185.85</v>
+        <v>80.7</v>
       </c>
       <c r="F6" t="n">
-        <v>51556.69</v>
+        <v>67126.75</v>
       </c>
       <c r="G6" t="n">
-        <v>14440.45999999999</v>
+        <v>9707.779999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1111.65</v>
+        <v>386.55</v>
       </c>
       <c r="I6" t="n">
-        <v>158961.1200000001</v>
+        <v>136157.7400000001</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>206469.09</v>
+        <v>223203.2799999999</v>
       </c>
       <c r="C7" t="n">
-        <v>62442.81</v>
+        <v>76662.02999999998</v>
       </c>
       <c r="D7" t="n">
-        <v>61650.59999999999</v>
+        <v>76491.59999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>792.21</v>
+        <v>170.43</v>
       </c>
       <c r="F7" t="n">
-        <v>50108.55000000002</v>
+        <v>63492.88</v>
       </c>
       <c r="G7" t="n">
-        <v>12334.26000000001</v>
+        <v>13169.15000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1132.61</v>
+        <v>1144.57</v>
       </c>
       <c r="I7" t="n">
-        <v>144026.28</v>
+        <v>146541.2499999999</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>232719.43</v>
+        <v>214823.8100000001</v>
       </c>
       <c r="C8" t="n">
-        <v>64810.07000000001</v>
+        <v>73485.12999999996</v>
       </c>
       <c r="D8" t="n">
-        <v>64513.37000000002</v>
+        <v>72245.64999999997</v>
       </c>
       <c r="E8" t="n">
-        <v>296.7</v>
+        <v>1239.48</v>
       </c>
       <c r="F8" t="n">
-        <v>52074.94999999999</v>
+        <v>61186.73000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>12735.12</v>
+        <v>12298.40000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1139.99</v>
+        <v>1110.71</v>
       </c>
       <c r="I8" t="n">
-        <v>167909.36</v>
+        <v>141338.6800000001</v>
       </c>
     </row>
     <row r="9">
@@ -694,31 +694,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239462.8699999999</v>
+        <v>204952.61</v>
       </c>
       <c r="C9" t="n">
-        <v>67639.74999999996</v>
+        <v>79025.42999999996</v>
       </c>
       <c r="D9" t="n">
-        <v>67335.08999999994</v>
+        <v>78365.46999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>304.66</v>
+        <v>659.96</v>
       </c>
       <c r="F9" t="n">
-        <v>55129.07</v>
+        <v>66736.75999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>12510.68</v>
+        <v>12288.67</v>
       </c>
       <c r="H9" t="n">
-        <v>1089.22</v>
+        <v>1137.8</v>
       </c>
       <c r="I9" t="n">
-        <v>171823.1199999999</v>
+        <v>125927.1800000001</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>